--- a/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N172_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T6321_W0022F0003T0006Z000C1N172_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>1.41985189223158</v>
+        <v>0.2307259324876317</v>
       </c>
       <c r="D2" t="n">
-        <v>8.793381980146204</v>
+        <v>1.428924571773758</v>
       </c>
       <c r="E2" t="n">
-        <v>13.25612500267236</v>
+        <v>2.154120312934258</v>
       </c>
       <c r="F2" t="n">
-        <v>13.63638213181058</v>
+        <v>2.215912096419218</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>44.43686002694399</v>
+        <v>7.220989754378398</v>
       </c>
       <c r="D3" t="n">
-        <v>44.81178875034256</v>
+        <v>7.281915671930665</v>
       </c>
       <c r="E3" t="n">
-        <v>13.25612500267236</v>
+        <v>2.154120312934258</v>
       </c>
       <c r="F3" t="n">
-        <v>13.63638213181058</v>
+        <v>2.215912096419218</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>21.08485208993226</v>
+        <v>3.426288464613993</v>
       </c>
       <c r="D4" t="n">
-        <v>21.5870331449229</v>
+        <v>3.507892886049972</v>
       </c>
       <c r="E4" t="n">
-        <v>13.25612500267236</v>
+        <v>2.154120312934258</v>
       </c>
       <c r="F4" t="n">
-        <v>13.63638213181058</v>
+        <v>2.215912096419218</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>31.18092365533773</v>
+        <v>5.066900093992381</v>
       </c>
       <c r="D5" t="n">
-        <v>30.90661511928292</v>
+        <v>5.022324956883475</v>
       </c>
       <c r="E5" t="n">
-        <v>13.25612500267236</v>
+        <v>2.154120312934258</v>
       </c>
       <c r="F5" t="n">
-        <v>13.63638213181058</v>
+        <v>2.215912096419218</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>21.37150596285615</v>
+        <v>3.472869718964125</v>
       </c>
       <c r="D6" t="n">
-        <v>6.964396824241635</v>
+        <v>1.131714483939266</v>
       </c>
       <c r="E6" t="n">
-        <v>13.25612500267236</v>
+        <v>2.154120312934258</v>
       </c>
       <c r="F6" t="n">
-        <v>13.63638213181058</v>
+        <v>2.215912096419218</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>15.42064516037039</v>
+        <v>2.505854838560189</v>
       </c>
       <c r="D7" t="n">
-        <v>10.75235642755541</v>
+        <v>1.747257919477754</v>
       </c>
       <c r="E7" t="n">
-        <v>13.25612500267236</v>
+        <v>2.154120312934258</v>
       </c>
       <c r="F7" t="n">
-        <v>13.63638213181058</v>
+        <v>2.215912096419218</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
